--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487588_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487588_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0322</v>
+        <v>5.0951</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5741</v>
+        <v>5.7733</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5419</v>
+        <v>-0.6781</v>
       </c>
       <c r="G2" t="n">
         <v>-0.779</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1411</v>
+        <v>1.204</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8214</v>
+        <v>1.0206</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3197</v>
+        <v>0.1834</v>
       </c>
       <c r="V2" t="n">
         <v>2.7298</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4958</v>
+        <v>3.4071</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9676</v>
+        <v>3.4697</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5282</v>
+        <v>-0.0626</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0954</v>
+        <v>1.6414</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9307</v>
+        <v>1.2877</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8353</v>
+        <v>0.3537</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0969</v>
+        <v>3.0118</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6374</v>
+        <v>1.6848</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5405</v>
+        <v>1.3269</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0015</v>
+        <v>-1.3704</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2933</v>
+        <v>-0.3971</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2948</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9825</v>
+        <v>-0.3522</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2752</v>
+        <v>0.2804</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2927</v>
+        <v>-0.6325</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>2.1179</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3338</v>
+        <v>3.2439</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0693</v>
+        <v>4.9671</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2645</v>
+        <v>-1.7232</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6414</v>
+        <v>3.1079</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2877</v>
+        <v>2.9116</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3537</v>
+        <v>0.1963</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0118</v>
+        <v>4.5392</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6848</v>
+        <v>3.3696</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3269</v>
+        <v>1.1696</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3704</v>
+        <v>-1.4313</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3971</v>
+        <v>-0.4581</v>
       </c>
       <c r="O4" t="n">
         <v>-0.9733000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4255</v>
+        <v>-0.5521</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.12</v>
+        <v>0.1741</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3055</v>
+        <v>-0.7262</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1179</v>
+        <v>-0.2821</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1179</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2612</v>
+        <v>2.695</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0662</v>
+        <v>2.1668</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8049</v>
+        <v>0.5282</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1079</v>
+        <v>3.0954</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9116</v>
+        <v>3.9307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1963</v>
+        <v>-0.8353</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5392</v>
+        <v>3.0969</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3696</v>
+        <v>3.6374</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1696</v>
+        <v>-0.5405</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4313</v>
+        <v>-0.0015</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4581</v>
+        <v>0.2933</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.2948</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5347</v>
+        <v>0.1817</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7268</v>
+        <v>0.4744</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.2927</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X5" t="n">
         <v>-1.506</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8667</v>
+        <v>1.885</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7254</v>
+        <v>1.8255</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1413</v>
+        <v>0.0595</v>
       </c>
       <c r="G6" t="n">
         <v>2.282</v>
@@ -922,13 +922,13 @@
         <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4437</v>
+        <v>-0.4253</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3831</v>
+        <v>-0.4649</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9418</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8235</v>
+        <v>0.9408</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7432</v>
+        <v>1.4373</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0803</v>
+        <v>-0.4965</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8575</v>
+        <v>-0.1687</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5561</v>
+        <v>-0.4301</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3014</v>
+        <v>0.2614</v>
       </c>
       <c r="J7" t="n">
-        <v>0.044</v>
+        <v>1.7909</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6055</v>
+        <v>0.4284</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6495</v>
+        <v>1.3625</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9015</v>
+        <v>-1.9596</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0494</v>
+        <v>-0.8585</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.951</v>
+        <v>-1.1011</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9049</v>
+        <v>-0.0547</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6992</v>
+        <v>0.6166</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2057</v>
+        <v>-0.6712</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7054</v>
+        <v>0.877</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3382</v>
+        <v>0.7422</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6328</v>
+        <v>0.1348</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1687</v>
+        <v>-0.8575</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4301</v>
+        <v>-0.5561</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2614</v>
+        <v>-0.3014</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7909</v>
+        <v>0.044</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4284</v>
+        <v>-0.6055</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3625</v>
+        <v>0.6495</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9596</v>
+        <v>-0.9015</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8585</v>
+        <v>0.0494</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1011</v>
+        <v>-0.951</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1344</v>
+        <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7099</v>
+        <v>0.9584</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5175</v>
+        <v>0.6982</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8075</v>
+        <v>0.2602</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4596</v>
+        <v>-0.2138</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3033</v>
+        <v>0.6036</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.763</v>
+        <v>-0.8175</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9476</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0119</v>
+        <v>0.2577</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1211</v>
+        <v>0.1792</v>
       </c>
       <c r="U10" t="n">
-        <v>0.133</v>
+        <v>0.0785</v>
       </c>
       <c r="V10" t="n">
         <v>0.2821</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6006</v>
+        <v>-0.4916</v>
       </c>
       <c r="E11" t="n">
         <v>0.6585</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2591</v>
+        <v>-1.1501</v>
       </c>
       <c r="G11" t="n">
         <v>1.2415</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2302</v>
+        <v>-0.1211</v>
       </c>
       <c r="T11" t="n">
         <v>-0.3028</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0727</v>
+        <v>0.1817</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1925</v>
+        <v>-0.6186</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6203</v>
+        <v>1.9216</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8128</v>
+        <v>-2.5402</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3975</v>
@@ -1390,13 +1390,13 @@
         <v>2.3284</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4188</v>
+        <v>0.155</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9691</v>
+        <v>0.3322</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4497</v>
+        <v>-0.1772</v>
       </c>
       <c r="V12" t="n">
         <v>1.1761</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7478</v>
+        <v>-2.3018</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8774</v>
+        <v>-1.3769</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8704</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1322</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1216</v>
+        <v>0.3244</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.424</v>
+        <v>0.0765</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3024</v>
+        <v>0.2479</v>
       </c>
       <c r="V13" t="n">
         <v>0.2821</v>
@@ -1507,10 +1507,10 @@
         <v>22.2699</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.8825</v>
+        <v>-7.882499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>5.760899999999999</v>
+        <v>5.760900000000001</v>
       </c>
       <c r="H14" t="n">
         <v>8.485900000000001</v>
@@ -1552,7 +1552,7 @@
         <v>3.588899999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.013</v>
+        <v>-2.012999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>4.1402</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.3734</v>
+        <v>9.028499999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8758</v>
+        <v>11.4764</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5023</v>
+        <v>-2.4478</v>
       </c>
       <c r="G15" t="n">
         <v>6.1868</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9462</v>
+        <v>-0.291</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4229</v>
+        <v>0.1777</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5233</v>
+        <v>-0.4688</v>
       </c>
       <c r="V15" t="n">
         <v>4.491</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0787</v>
+        <v>2.9057</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0766</v>
+        <v>2.8764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0021</v>
+        <v>0.0293</v>
       </c>
       <c r="G16" t="n">
         <v>2.6493</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3946</v>
+        <v>-0.5675</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1828</v>
+        <v>-0.0174</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5774</v>
+        <v>-0.5501</v>
       </c>
       <c r="V16" t="n">
         <v>0.0478</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.175</v>
+        <v>0.2751</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5355</v>
+        <v>-0.4354</v>
       </c>
       <c r="F17" t="n">
         <v>0.7105</v>
@@ -1780,10 +1780,10 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0482</v>
+        <v>0.1483</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U17" t="n">
         <v>0.1694</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0805</v>
+        <v>-0.6474</v>
       </c>
       <c r="E18" t="n">
-        <v>0.368</v>
+        <v>-0.3327</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2874</v>
+        <v>-0.3147</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7598</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9284</v>
+        <v>0.2005</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9107</v>
+        <v>0.21</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0177</v>
+        <v>-0.0095</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2821</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-1.6239</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2888</v>
+        <v>3.9885</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.2581</v>
+        <v>-5.6124</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7085</v>
@@ -1936,13 +1936,13 @@
         <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7093</v>
+        <v>0.0547</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0329</v>
+        <v>0.7326</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3236</v>
+        <v>-0.678</v>
       </c>
       <c r="V19" t="n">
         <v>-1.9104</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.15</v>
+        <v>-3.4503</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1042</v>
+        <v>-0.1961</v>
       </c>
       <c r="F20" t="n">
         <v>-3.2542</v>
@@ -2014,10 +2014,10 @@
         <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5462</v>
+        <v>0.2459</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9724</v>
+        <v>0.6721</v>
       </c>
       <c r="U20" t="n">
         <v>-0.4262</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8795</v>
+        <v>-4.6431</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9597</v>
+        <v>-1.8596</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9198</v>
+        <v>-2.7835</v>
       </c>
       <c r="G21" t="n">
         <v>-2.726</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.867</v>
+        <v>-0.6306</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0595</v>
+        <v>0.0406</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8075</v>
+        <v>-0.6712</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1224</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2247</v>
+        <v>-4.9067</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8937</v>
+        <v>-2.7424</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.331</v>
+        <v>-2.1643</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.749</v>
+        <v>-4.544</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1639</v>
+        <v>-0.8659</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5851</v>
+        <v>-3.6781</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2281</v>
+        <v>-1.8672</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9845</v>
+        <v>0.7209</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2436</v>
+        <v>-2.5881</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9771</v>
+        <v>-2.6768</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1485</v>
+        <v>-1.5868</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8286</v>
+        <v>-1.09</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7164</v>
+        <v>0.194</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.8508</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1344</v>
+        <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4607</v>
+        <v>0.0552</v>
       </c>
       <c r="T22" t="n">
-        <v>0.729</v>
+        <v>0.095</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1897</v>
+        <v>-0.0398</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2985</v>
+        <v>-0.6119</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2985</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7437</v>
+        <v>-5.5617</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4431</v>
+        <v>-3.3942</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3006</v>
+        <v>-2.1675</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.544</v>
+        <v>-0.749</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8659</v>
+        <v>-0.1639</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6781</v>
+        <v>-0.5851</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8672</v>
+        <v>1.2281</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7209</v>
+        <v>0.9845</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5881</v>
+        <v>0.2436</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6768</v>
+        <v>-1.9771</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5868</v>
+        <v>-1.1485</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.09</v>
+        <v>-0.8286</v>
       </c>
       <c r="P23" t="n">
-        <v>0.194</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9702</v>
+        <v>-4.8508</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1642</v>
+        <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7817</v>
+        <v>-0.7977</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6057</v>
+        <v>0.2285</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1761</v>
+        <v>-1.0262</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6119</v>
+        <v>-1.2985</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6119</v>
+        <v>-1.2985</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1279</v>
+        <v>-5.6635</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.999</v>
+        <v>-1.3984</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1289</v>
+        <v>-4.2652</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0701</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3578</v>
+        <v>0.1065</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6057</v>
+        <v>-0.0051</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2479</v>
+        <v>0.1116</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7298</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.3875</v>
+        <v>-14.2873</v>
       </c>
       <c r="E25" t="n">
-        <v>7.882400000000001</v>
+        <v>7.9825</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.2697</v>
+        <v>-22.2698</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.7609</v>
+        <v>-5.760899999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-8.485799999999999</v>
@@ -2395,7 +2395,7 @@
         <v>-9.620899999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.910500000000001</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.4928</v>
@@ -2404,10 +2404,10 @@
         <v>13.5823</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5759</v>
+        <v>-1.4757</v>
       </c>
       <c r="T25" t="n">
-        <v>2.0129</v>
+        <v>2.113</v>
       </c>
       <c r="U25" t="n">
         <v>-3.5888</v>
